--- a/bom.xlsx
+++ b/bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CODING\biometric access door lock system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC06DDE-06CE-4AE5-9889-47074933B71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ADA3A4-3769-446D-B2CD-EBFE29EEB42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="4425" windowWidth="16425" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="3135" windowWidth="16425" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>S. No.</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>sourced by me</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>https://robocraze.com/products/1n4007-diode-pack-of-10?_pos=1&amp;_sid=7c56ba663&amp;_ss=r</t>
   </si>
 </sst>
 </file>
@@ -622,19 +628,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -642,24 +648,39 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">

--- a/bom.xlsx
+++ b/bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CODING\biometric access door lock system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ADA3A4-3769-446D-B2CD-EBFE29EEB42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CB6CEC-0860-4DA9-86D7-2EC6D4845EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="3135" windowWidth="16425" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>ESP32</t>
   </si>
   <si>
-    <t>https://robocraze.com/products/nodemcu-32-wifi-bluetooth-esp32-development-board30-pin?_pos=1&amp;_sid=b3279d971&amp;_ss=r</t>
-  </si>
-  <si>
     <t>Fingerprint Scanner Module</t>
   </si>
   <si>
@@ -118,6 +115,9 @@
   </si>
   <si>
     <t>https://robocraze.com/products/1n4007-diode-pack-of-10?_pos=1&amp;_sid=7c56ba663&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://robocraze.com/products/esp32-development-board?_pos=1&amp;_psq=esp&amp;_psid=ffe363e30&amp;_ss=e</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
@@ -480,7 +480,7 @@
         <v>399</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -488,7 +488,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>912</v>
@@ -500,7 +500,7 @@
         <v>912</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -508,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>139</v>
@@ -520,7 +520,7 @@
         <v>139</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -528,7 +528,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>369</v>
@@ -540,7 +540,7 @@
         <v>369</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -548,7 +548,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -560,7 +560,7 @@
         <v>180</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -568,7 +568,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>89</v>
@@ -580,7 +580,7 @@
         <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -588,7 +588,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>48</v>
@@ -600,7 +600,7 @@
         <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -608,7 +608,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>14</v>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -628,7 +628,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>15</v>
@@ -640,7 +640,7 @@
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -668,7 +668,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -680,27 +680,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/bom.xlsx
+++ b/bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CODING\biometric access door lock system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CB6CEC-0860-4DA9-86D7-2EC6D4845EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B32A044-A748-4D15-A4FF-404312B291C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12510" yWindow="5640" windowWidth="16425" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,10 +124,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -150,13 +158,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -479,7 +490,7 @@
       <c r="E2">
         <v>399</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -519,7 +530,7 @@
       <c r="E4">
         <v>139</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -559,7 +570,7 @@
       <c r="E6">
         <v>180</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -579,7 +590,7 @@
       <c r="E7">
         <v>89</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -599,7 +610,7 @@
       <c r="E8">
         <v>48</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -619,7 +630,7 @@
       <c r="E9">
         <v>14</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -639,7 +650,7 @@
       <c r="E10">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -684,6 +695,15 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{694189CA-5F6C-4CCE-B547-B31C24F2B7A4}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{2517A6F4-349B-4FFB-ABB8-F5C105BE501A}"/>
+    <hyperlink ref="F10" r:id="rId3" xr:uid="{03EA4277-93EA-415A-93D7-D16943F38C2C}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{CC031B88-5A5A-4B9B-8F60-FA4A7156F9ED}"/>
+    <hyperlink ref="F8" r:id="rId5" xr:uid="{AEA103D9-7D66-4DEB-8B9F-D725BC984BD5}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{FDAF4753-3128-4F26-80E6-6D5CA5420A36}"/>
+    <hyperlink ref="F6" r:id="rId7" xr:uid="{E2E43AA5-FC0D-4827-B1D3-7AB9661F89B6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>